--- a/Monitoramento_Indicadores.xlsx
+++ b/Monitoramento_Indicadores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://governosp.sharepoint.com/teams/DETRAN-CoordenadoriadeSeguranaViria/Shared Documents/DSV-CGSV - COST - DRML/3. Produção/1. Projetos Estratégicos/1. PSV/2. Monitoramento/9. Painel/Bases/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1401" documentId="8_{1ABC2F2F-E795-4630-81E6-C73ED639B81B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{37EE322C-877D-4E0C-946B-6D0FFE11DAFA}"/>
+  <xr:revisionPtr revIDLastSave="1412" documentId="8_{1ABC2F2F-E795-4630-81E6-C73ED639B81B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F86B167E-B11D-4A7A-BE94-2B617A83A73B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{629E1BA9-476E-4EE4-BD56-2392CAE20BB2}"/>
   </bookViews>
@@ -16859,7 +16859,9 @@
       </c>
       <c r="N177" s="24"/>
       <c r="O177" s="24"/>
-      <c r="P177" s="25"/>
+      <c r="P177" s="25">
+        <v>5</v>
+      </c>
       <c r="Q177" s="25">
         <v>5</v>
       </c>
@@ -27254,7 +27256,7 @@
   </sheetData>
   <autoFilter ref="A1:S366" xr:uid="{F6D77FC8-948A-4DB3-85AA-85145AB39F87}"/>
   <phoneticPr fontId="16" type="noConversion"/>
-  <dataValidations disablePrompts="1" count="20">
+  <dataValidations count="20">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K330:K366" xr:uid="{7741C6D4-A24C-48CE-8024-4763EEB58F60}">
       <formula1>"SES-SP,SSP,Secretarias municipais de saúde,Órgaos Municipais,Detran-SP,Academia,Institutos de Pesquisa,SECOM,ARTESP,SEDS,SEDPcD,DER-SP"</formula1>
     </dataValidation>
@@ -27321,6 +27323,28 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Status xmlns="31067d2d-e48e-4508-aa64-80d1f142e7dc" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="31067d2d-e48e-4508-aa64-80d1f142e7dc">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ee1a5240-fbb3-422c-a5c8-d7a8e3758d68" xsi:nil="true"/>
+    <AULA xmlns="31067d2d-e48e-4508-aa64-80d1f142e7dc" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E7EE74678CDAA749BF87014A2B4560BF" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d027820d0036d222697a6ff7b3f5c47a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="31067d2d-e48e-4508-aa64-80d1f142e7dc" xmlns:ns3="ee1a5240-fbb3-422c-a5c8-d7a8e3758d68" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a4c4f1818ba5fd5562b618916876c884" ns2:_="" ns3:_="">
     <xsd:import namespace="31067d2d-e48e-4508-aa64-80d1f142e7dc"/>
@@ -27551,29 +27575,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8576A815-E8FB-4811-A9CF-9B9773A8FDFC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="31067d2d-e48e-4508-aa64-80d1f142e7dc"/>
+    <ds:schemaRef ds:uri="ee1a5240-fbb3-422c-a5c8-d7a8e3758d68"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Status xmlns="31067d2d-e48e-4508-aa64-80d1f142e7dc" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="31067d2d-e48e-4508-aa64-80d1f142e7dc">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ee1a5240-fbb3-422c-a5c8-d7a8e3758d68" xsi:nil="true"/>
-    <AULA xmlns="31067d2d-e48e-4508-aa64-80d1f142e7dc" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1026D056-C258-4621-818E-7608477D7483}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF385CF-1629-4F63-AEB5-B16674D81DBA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -27590,23 +27611,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1026D056-C258-4621-818E-7608477D7483}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8576A815-E8FB-4811-A9CF-9B9773A8FDFC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="31067d2d-e48e-4508-aa64-80d1f142e7dc"/>
-    <ds:schemaRef ds:uri="ee1a5240-fbb3-422c-a5c8-d7a8e3758d68"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>